--- a/artfynd/A 23161-2023 artfynd.xlsx
+++ b/artfynd/A 23161-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23161-2023 artfynd.xlsx
+++ b/artfynd/A 23161-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,108 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120355778</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79491</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6441</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Slanklav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Collema flaccidum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hednäset, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>598441</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6679672</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23161-2023 artfynd.xlsx
+++ b/artfynd/A 23161-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,6 +890,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121981164</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91343</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ista Naturreservat , Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598260</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6679424</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera och allt skall huggas inom reservatet!!?</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23161-2023 artfynd.xlsx
+++ b/artfynd/A 23161-2023 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>121981164</v>
       </c>
       <c r="B4" t="n">
-        <v>91343</v>
+        <v>91357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23161-2023 artfynd.xlsx
+++ b/artfynd/A 23161-2023 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>121981164</v>
       </c>
       <c r="B4" t="n">
-        <v>91394</v>
+        <v>91404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23161-2023 artfynd.xlsx
+++ b/artfynd/A 23161-2023 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>121981164</v>
       </c>
       <c r="B4" t="n">
-        <v>91404</v>
+        <v>91416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23161-2023 artfynd.xlsx
+++ b/artfynd/A 23161-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97604642</v>
+        <v>191913</v>
       </c>
       <c r="B2" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>530</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dichelyma capillaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ista naturreservat, Gstr</t>
+          <t>Ista NR, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598413.8381654313</v>
+        <v>598481</v>
       </c>
       <c r="R2" t="n">
-        <v>6679470.638966227</v>
+        <v>6679515</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,73 +756,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>stambas</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
-        </is>
-      </c>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120355778</v>
+        <v>421562</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6441</v>
+        <v>962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Strandskinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Leptogium rivulare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Mont.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hednäset, Gstr</t>
+          <t>Mälholmen, Hamre i Irstamyren, 6 km SSV Österfärnebo k:a., Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598441</v>
+        <v>598152</v>
       </c>
       <c r="R3" t="n">
-        <v>6679672</v>
+        <v>6679584</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>1993-04-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>1993-04-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,72 +858,88 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Populus (1 träd) i kantzonen mot granplantering.</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121981164</v>
+        <v>425690</v>
       </c>
       <c r="B4" t="n">
-        <v>91416</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Strandskinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium rivulare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Mont.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ista Naturreservat , Gstr</t>
+          <t>Hednäset/Hamreholmen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598260</v>
+        <v>598450</v>
       </c>
       <c r="R4" t="n">
-        <v>6679424</v>
+        <v>6679730</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,17 +963,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera och allt skall huggas inom reservatet!!?</t>
+          <t>Gammal aspbas</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,22 +982,1125 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Myrholme</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>425691</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>962</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Strandskinnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leptogium rivulare</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Mont.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hednäset/Hamreholmen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>598456</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6679717</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2010-08-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2010-08-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Nationalpark</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Myrholme</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>425692</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>962</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Strandskinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium rivulare</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Mont.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hednäset/Hamreholmen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598463</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6679705</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2010-08-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2010-08-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Grov aspbas</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Myrholme</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16922240</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>962</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Strandskinnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptogium rivulare</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Mont.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Österfärnebo, Istamyran / Hamreholmen. Gästrikland., Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>598451</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6679706</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2014-12-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2014-12-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Myrholme med gles bård av aspsvämskog, älvnära.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stambark av grov asp i svämhöjd</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97604626</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>962</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Strandskinnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptogium rivulare</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Mont.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ista naturreservat, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598459</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6679725</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>betad svämaspskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>grov aspbas</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97604627</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>962</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Strandskinnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leptogium rivulare</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Mont.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ista naturreservat, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>598459</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6679729</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>små bålar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>betad svämaspskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>grov aspbas</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121981164</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92564</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ista Naturreservat , Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>598260</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6679424</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flera och allt skall huggas inom reservatet!!?</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97604642</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ista naturreservat, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>598414</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6679470</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97604639</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ista naturreservat, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>598149</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6679581</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120355778</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80300</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6441</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Slanklav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Collema flaccidum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hednäset, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>598441</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6679672</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>97604625</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ista naturreservat, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>598466</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6679697</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23161-2023 artfynd.xlsx
+++ b/artfynd/A 23161-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/191913</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/421562</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/425690</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/425691</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/425692</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16922240</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97604626</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1593,6 +1633,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97604627</t>
         </is>
       </c>
     </row>
@@ -1701,6 +1746,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121981164</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1802,6 +1852,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97604642</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97604639</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120355778</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2101,8 +2166,28 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97604625</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>